--- a/reduced_participant_table.xlsx
+++ b/reduced_participant_table.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -465,80 +465,85 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>age</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>postpartum_weeks</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>children_count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>statut</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>seances</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>clarite</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>respect_consignes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>satisfaction_seance</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>confiance</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>recommandation</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>n_formulaires_suivi</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>completion_suivi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>satisfaction_generale_algorithme</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>nombre_problemes_algorithme</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>nombre_sessions_nolio</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>reached_30min_ever</t>
         </is>
@@ -548,54 +553,59 @@
       <c r="A2" t="n">
         <v>1550</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="D2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>pas valide</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>2.5</v>
-      </c>
       <c r="G2" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N2" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="N2" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="O2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>22</v>
       </c>
-      <c r="Q2" t="b">
+      <c r="R2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -603,54 +613,59 @@
       <c r="A3" t="n">
         <v>2334</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="D3" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>pas valide</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>0.75</v>
-      </c>
       <c r="G3" s="2" t="n">
-        <v>3.833333333333333</v>
+        <v>0.9</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2.916666666666667</v>
+        <v>3.9</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M3" t="n">
         <v>10</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="N3" s="2" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="O3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="b">
+      <c r="P3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -658,54 +673,59 @@
       <c r="A4" t="n">
         <v>2500</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="D4" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>valide</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>1.857142857142857</v>
-      </c>
       <c r="G4" s="2" t="n">
-        <v>2.857142857142857</v>
+        <v>3.25</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>2.857142857142857</v>
+        <v>5</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.428571428571428</v>
+        <v>3.5</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2.857142857142857</v>
-      </c>
-      <c r="L4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
         <v>4</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="N4" s="2" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="O4" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
+      <c r="P4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -713,54 +733,59 @@
       <c r="A5" t="n">
         <v>2729</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="D5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>valide</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>0.65</v>
-      </c>
       <c r="G5" s="2" t="n">
-        <v>0.85</v>
+        <v>3.25</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.75</v>
+        <v>4.25</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.95</v>
+        <v>3.75</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.9</v>
+        <v>4.75</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="L5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>4.875</v>
+      </c>
+      <c r="M5" t="n">
         <v>2</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="N5" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="O5" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="O5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="P5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
         <v>7</v>
       </c>
-      <c r="Q5" t="b">
+      <c r="R5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -768,54 +793,59 @@
       <c r="A6" t="n">
         <v>3357</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="D6" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="E6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>pas valide</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="G6" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="n">
         <v>4</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="N6" s="2" t="n">
         <v>0.4</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="O6" s="2" t="n">
         <v>4.75</v>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="b">
+      <c r="P6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -823,54 +853,59 @@
       <c r="A7" t="n">
         <v>3401</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="D7" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="E7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>pas valide</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="G7" s="2" t="n">
-        <v>1.1875</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.25</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1.8125</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.75</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L7" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="M7" t="n">
         <v>3</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="N7" s="2" t="n">
         <v>0.375</v>
       </c>
-      <c r="N7" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="O7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="b">
+        <v>5</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -878,54 +913,59 @@
       <c r="A8" t="n">
         <v>3476</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="D8" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>pas valide</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>2.571428571428572</v>
-      </c>
       <c r="G8" s="2" t="n">
-        <v>2.714285714285714</v>
+        <v>4.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2.428571428571428</v>
+        <v>4.75</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2.428571428571428</v>
+        <v>4.25</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.857142857142857</v>
+        <v>4.25</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2.857142857142857</v>
-      </c>
-      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="n">
         <v>4</v>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="N8" s="2" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="O8" s="2" t="n">
         <v>4.75</v>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="P8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="n">
         <v>7</v>
       </c>
-      <c r="Q8" t="b">
+      <c r="R8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -933,54 +973,59 @@
       <c r="A9" t="n">
         <v>3693</v>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>30</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="C9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>valide</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
-        <v>1.6</v>
-      </c>
       <c r="G9" s="2" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5</v>
-      </c>
-      <c r="M9" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="b">
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -988,54 +1033,59 @@
       <c r="A10" t="n">
         <v>4704</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="D10" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>pas valide</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" s="2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.625</v>
+        <v>4</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.625</v>
+        <v>5</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="2" t="n">
         <v>0.125</v>
       </c>
-      <c r="N10" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="O10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>7</v>
       </c>
-      <c r="Q10" t="b">
+      <c r="R10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1043,54 +1093,59 @@
       <c r="A11" t="n">
         <v>5579</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="D11" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="E11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>pas valide</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
-        <v>1.5</v>
-      </c>
       <c r="G11" s="2" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" t="n">
         <v>3</v>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="N11" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="O11" s="2" t="n">
         <v>2.75</v>
       </c>
-      <c r="O11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="b">
+      <c r="P11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1098,54 +1153,59 @@
       <c r="A12" t="n">
         <v>5801</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="D12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>valide</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="G12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="J12" s="2" t="n">
         <v>4.833333333333333</v>
       </c>
-      <c r="J12" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="K12" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" t="n">
         <v>6</v>
       </c>
-      <c r="M12" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="N12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="O12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="P12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>20</v>
       </c>
-      <c r="Q12" t="b">
+      <c r="R12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1153,54 +1213,59 @@
       <c r="A13" t="n">
         <v>6018</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="D13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>pas valide</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>4.4</v>
-      </c>
       <c r="G13" s="2" t="n">
-        <v>4.5</v>
+        <v>4.888888888888889</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>4.5</v>
+        <v>4.777777777777778</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" t="n">
         <v>9</v>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="N13" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="N13" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="O13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="b">
+        <v>5</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1208,23 +1273,25 @@
       <c r="A14" t="n">
         <v>6205</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="D14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>valide</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="G14" s="2" t="n">
         <v>5</v>
       </c>
@@ -1240,22 +1307,25 @@
       <c r="K14" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" t="n">
         <v>6</v>
       </c>
-      <c r="M14" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="N14" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
+        <v>5</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>22</v>
       </c>
-      <c r="Q14" t="b">
+      <c r="R14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1263,54 +1333,59 @@
       <c r="A15" t="n">
         <v>6302</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="D15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="E15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>valide</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="G15" s="2" t="n">
-        <v>1.1</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.4</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.2</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" t="n">
         <v>3</v>
       </c>
-      <c r="M15" s="2" t="n">
+      <c r="N15" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="O15" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="O15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="b">
+      <c r="P15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1318,54 +1393,59 @@
       <c r="A16" t="n">
         <v>6487</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="D16" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="E16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>valide</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="G16" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="H16" s="2" t="n">
         <v>4.666666666666667</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="I16" s="2" t="n">
         <v>4.333333333333333</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="J16" s="2" t="n">
         <v>4.5</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>4.833333333333333</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>4.833333333333333</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="2" t="n">
+        <v>4.833333333333333</v>
+      </c>
+      <c r="M16" t="n">
         <v>6</v>
       </c>
-      <c r="M16" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="N16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="2" t="n">
         <v>4.75</v>
       </c>
-      <c r="O16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="b">
+      <c r="P16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1373,54 +1453,59 @@
       <c r="A17" t="n">
         <v>6509</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="D17" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="E17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>valide</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="G17" s="2" t="n">
         <v>3.571428571428572</v>
       </c>
-      <c r="G17" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="H17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" s="2" t="n">
         <v>3.857142857142857</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="J17" s="2" t="n">
         <v>3.428571428571428</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="K17" s="2" t="n">
         <v>3.285714285714286</v>
       </c>
-      <c r="K17" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="L17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" t="n">
         <v>7</v>
       </c>
-      <c r="M17" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="N17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="O17" s="2" t="n">
+      <c r="P17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="b">
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1428,52 +1513,57 @@
       <c r="A18" t="n">
         <v>6557</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="D18" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
         <is>
           <t>valide</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
-        <v>2.833333333333333</v>
-      </c>
       <c r="G18" s="2" t="n">
-        <v>1.833333333333333</v>
+        <v>3.4</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="L18" t="n">
-        <v>5</v>
-      </c>
-      <c r="M18" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M18" t="n">
+        <v>5</v>
+      </c>
+      <c r="N18" s="2" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="O18" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="O18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="P18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>11</v>
       </c>
-      <c r="Q18" t="b">
+      <c r="R18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1481,54 +1571,59 @@
       <c r="A19" t="n">
         <v>6841</v>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="D19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="E19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>pas valide</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n">
-        <v>4.142857142857143</v>
-      </c>
       <c r="G19" s="2" t="n">
-        <v>4.285714285714286</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>4.285714285714286</v>
+        <v>5</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>4.285714285714286</v>
+        <v>5</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4.285714285714286</v>
+        <v>5</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>4.285714285714286</v>
-      </c>
-      <c r="L19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" t="n">
         <v>6</v>
       </c>
-      <c r="M19" s="2" t="n">
+      <c r="N19" s="2" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="O19" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="O19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="P19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>23</v>
       </c>
-      <c r="Q19" t="b">
+      <c r="R19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1536,54 +1631,59 @@
       <c r="A20" t="n">
         <v>6845</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="D20" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>valide</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
-        <v>2.285714285714286</v>
-      </c>
       <c r="G20" s="2" t="n">
-        <v>3.571428571428572</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2.714285714285714</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3.428571428571428</v>
+        <v>3.5</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>3.785714285714286</v>
-      </c>
-      <c r="L20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>4.416666666666667</v>
+      </c>
+      <c r="M20" t="n">
         <v>6</v>
       </c>
-      <c r="M20" s="2" t="n">
+      <c r="N20" s="2" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="O20" s="2" t="n">
         <v>4.75</v>
       </c>
-      <c r="O20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="b">
+      <c r="P20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1591,54 +1691,59 @@
       <c r="A21" t="n">
         <v>6961</v>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="D21" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="E21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>pas valide</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="G21" s="2" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" t="n">
         <v>2</v>
       </c>
-      <c r="M21" s="2" t="n">
+      <c r="N21" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="O21" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="O21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="b">
+      <c r="P21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1646,54 +1751,59 @@
       <c r="A22" t="n">
         <v>7050</v>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>3</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>pas valide</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
-        <v>3.75</v>
-      </c>
       <c r="G22" s="2" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>3.625</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L22" t="n">
+        <v>4.833333333333333</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="M22" t="n">
         <v>6</v>
       </c>
-      <c r="M22" s="2" t="n">
+      <c r="N22" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="N22" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="O22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
+        <v>5</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>24</v>
       </c>
-      <c r="Q22" t="b">
+      <c r="R22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1701,54 +1811,59 @@
       <c r="A23" t="n">
         <v>7072</v>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="D23" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="E23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>valide</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n">
-        <v>2.3</v>
-      </c>
       <c r="G23" s="2" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L23" t="n">
-        <v>5</v>
-      </c>
-      <c r="M23" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M23" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="O23" s="2" t="n">
         <v>4.75</v>
       </c>
-      <c r="O23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="b">
+      <c r="P23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1756,54 +1871,59 @@
       <c r="A24" t="n">
         <v>8441</v>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="D24" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>pas valide</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="G24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" s="2" t="n">
         <v>0.375</v>
       </c>
-      <c r="G24" s="2" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="L24" t="n">
-        <v>3</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="O24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
+        <v>5</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>10</v>
       </c>
-      <c r="Q24" t="b">
+      <c r="R24" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1811,54 +1931,59 @@
       <c r="A25" t="n">
         <v>8865</v>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="D25" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>valide</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n">
-        <v>3.571428571428572</v>
-      </c>
       <c r="G25" s="2" t="n">
-        <v>4.285714285714286</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>4.285714285714286</v>
+        <v>5</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>4.285714285714286</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L25" t="n">
+        <v>5</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="M25" t="n">
         <v>6</v>
       </c>
-      <c r="M25" s="2" t="n">
+      <c r="N25" s="2" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="O25" s="2" t="n">
         <v>4.75</v>
       </c>
-      <c r="O25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="P25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>28</v>
       </c>
-      <c r="Q25" t="b">
+      <c r="R25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1866,50 +1991,55 @@
       <c r="A26" t="n">
         <v>9246</v>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="D26" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="E26" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>pas valide</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="G26" s="2" t="n">
-        <v>4.285714285714286</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>4.142857142857143</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>4.142857142857143</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>4.285714285714286</v>
-      </c>
-      <c r="L26" t="n">
+        <v>4.833333333333333</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M26" t="n">
         <v>6</v>
       </c>
-      <c r="M26" s="2" t="n">
+      <c r="N26" s="2" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="n">
         <v>19</v>
       </c>
-      <c r="Q26" t="b">
+      <c r="R26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1917,54 +2047,59 @@
       <c r="A27" t="n">
         <v>9884</v>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="D27" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>pas valide</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n">
-        <v>2.285714285714286</v>
-      </c>
       <c r="G27" s="2" t="n">
-        <v>3.571428571428572</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>3.142857142857143</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>3</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>3.428571428571428</v>
+        <v>3.5</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>3.428571428571428</v>
-      </c>
-      <c r="L27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M27" t="n">
         <v>6</v>
       </c>
-      <c r="M27" s="2" t="n">
+      <c r="N27" s="2" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N27" s="2" t="n">
+      <c r="O27" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="O27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="P27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>7</v>
       </c>
-      <c r="Q27" t="b">
+      <c r="R27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1972,54 +2107,59 @@
       <c r="A28" t="n">
         <v>9909</v>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="D28" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="E28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>pas valide</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="G28" s="2" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M28" t="n">
         <v>2</v>
       </c>
-      <c r="M28" s="2" t="n">
+      <c r="N28" s="2" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N28" s="2" t="n">
+      <c r="O28" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="O28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="b">
+      <c r="P28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2027,50 +2167,55 @@
       <c r="A29" t="n">
         <v>9921</v>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="D29" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>valide</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>1.7</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="H29" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="I29" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="I29" s="2" t="n">
+      <c r="J29" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="J29" s="2" t="n">
+      <c r="K29" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="K29" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="L29" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M29" t="n">
         <v>10</v>
       </c>
-      <c r="M29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="b">
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="b">
         <v>0</v>
       </c>
     </row>
